--- a/海外メンタルヘルスAI_未上陸サービス調査_2026.xlsx
+++ b/海外メンタルヘルスAI_未上陸サービス調査_2026.xlsx
@@ -1565,7 +1565,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>FDAクリアランス＋メディケア償還モデル。日本に対応する償還経路がない</t>
+          <t>FDAクリアランス＋メディケア償還モデル。日本にも保険収載の前例（Medcle等）はあるが製品ごとの個別承認が必要</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>メンタルヘルス領域のAI／デジタル治療について、日本に広く使われる償還経路がまだ確立していない</t>
+          <t>デジタル治療の保険収載は日本にも存在する（Medcle＝不眠障害、CureApp＝禁煙・高血圧・減酒等）。ただし製品単位で治験・薬事承認・保険収載を通す必要があり、メンタルヘルス領域の生成AIへの適用事例は確認できていない</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>エビデンス面では最有力だが、日本に償還の受け皿がないことが決定的な制約</t>
+          <t>エビデンス面では最有力。日本にも保険収載の前例（Medcle等）はあるが、製品ごとの治験＋薬事承認＋保険収載が必要で個人・小規模開発には現実的でない</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -4432,7 +4432,7 @@
         <is>
           <t>【空白③】処方型デジタル治療
 （Big Health／HelloBetter）
-※償還経路がなく保留</t>
+※個別承認が必要で保留</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -5719,7 +5719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5840,6 +5840,22 @@
       </c>
       <c r="D9" s="5" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>【訂正 2026-10-04】初版では「日本に償還の受け皿がない」と記載しましたが誤りでした</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>日本にもデジタル治療の保険収載はあります（Medcle＝不眠障害、CureApp＝禁煙・高血圧・減酒等）。ただし製品ごとの個別承認が必要で、個人・小規模開発の対象外という結論は変わりません。該当箇所は修正済み</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
